--- a/AAII_Financials/Quarterly/CIIHY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CIIHY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="92">
   <si>
     <t>CIIHY</t>
   </si>
@@ -656,76 +656,79 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -771,8 +774,11 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -818,8 +824,11 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -865,8 +874,11 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -884,8 +896,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -931,8 +944,11 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -978,8 +994,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1025,8 +1044,11 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1072,8 +1094,11 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1088,8 +1113,9 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1135,8 +1161,11 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1182,8 +1211,11 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1201,8 +1233,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1248,8 +1281,11 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1295,8 +1331,11 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1342,8 +1381,11 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1389,8 +1431,11 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1436,8 +1481,11 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1483,8 +1531,11 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1530,8 +1581,11 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1577,8 +1631,11 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1624,8 +1681,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1671,8 +1731,11 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1718,8 +1781,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1765,8 +1831,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1812,8 +1881,11 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1859,8 +1931,11 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1906,8 +1981,11 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1953,60 +2031,66 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2024,8 +2108,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2043,431 +2128,459 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>15267700</v>
+      </c>
+      <c r="E41" s="3">
         <v>12856500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13511000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>62170400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11397000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>44344200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>14255000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>49607700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11171900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>46305600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>42701600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>39346400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>16534400</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q41" s="3">
+      <c r="Q41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R41" s="3">
         <v>45849600</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>213220000</v>
+      </c>
+      <c r="E42" s="3">
         <v>191408600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>177721900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>124682000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>159624400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>120412100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>143952800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>120437100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>97492600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>105028100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>101540000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>100559100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>91526400</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>86817000</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>62510900</v>
+      </c>
+      <c r="E43" s="3">
         <v>50580200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>46208300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>45276900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>34188900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>34143900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>28191100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>34157600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>25783900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>26471200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>25336700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>24451800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>24824300</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q43" s="3">
+      <c r="Q43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R43" s="3">
         <v>23513800</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3">
         <v>557700</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3">
         <v>282100</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3">
         <v>200100</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3">
         <v>150000</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N44" s="3">
         <v>185400</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O44" s="3">
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3">
         <v>38100</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q44" s="3">
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R44" s="3">
         <v>89800</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>43083900</v>
+      </c>
+      <c r="E45" s="3">
         <v>38404500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>27399700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>27013700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>21103600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>21947800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>18585400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>18318100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>46698300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>15084600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>16413200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5835000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>47718700</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R45" s="3">
         <v>16666800</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>334082500</v>
+      </c>
+      <c r="E46" s="3">
         <v>293249800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>265398600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>259143000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>226596100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>220847900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>205184400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>222520500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>181296700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>192889400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>186176900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>170192300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>180642000</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q46" s="3">
+      <c r="Q46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R46" s="3">
         <v>172937000</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>21191200</v>
+      </c>
+      <c r="E47" s="3">
         <v>27469500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>27300900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>20925300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>18271000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>21381900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>24731600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>20376300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>16092900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>19197800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8581800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>9427500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>5095100</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R47" s="3">
         <v>7831000</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1627100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1577600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1584200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1536100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1488200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1419000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1430000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1545100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1514100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1542700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1579700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1510400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1434000</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q48" s="3">
+      <c r="Q48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R48" s="3">
         <v>1482500</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1700800</v>
+      </c>
+      <c r="E49" s="3">
         <v>1684600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1669200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1634500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1630800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1614400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1612600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1665700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1612200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1627200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1662900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1602100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1616700</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
-      </c>
       <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
         <v>1718500</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2513,8 +2626,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2560,55 +2676,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4029400</v>
+      </c>
+      <c r="E52" s="3">
         <v>120100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>262500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>119600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3113500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>119300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>291400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>126100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4361700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1034000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5965300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9580800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6344100</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q52" s="3">
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R52" s="3">
         <v>4039600</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2654,55 +2776,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>363609800</v>
+      </c>
+      <c r="E54" s="3">
         <v>325437800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>297652800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>284626000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>252342400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>246577700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>234372800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>246876600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>205728900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>217066700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>204961200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>193627300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>196618900</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q54" s="3">
+      <c r="Q54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R54" s="3">
         <v>189729700</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2720,8 +2848,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2739,290 +2868,309 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13356200</v>
+      </c>
+      <c r="E57" s="3">
         <v>37940100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8747200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>34082500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6600200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>27203400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5352800</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L57" s="3">
         <v>4651600</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N57" s="3">
         <v>4687800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>27250800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6487900</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q57" s="3">
+      <c r="Q57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R57" s="3">
         <v>6160600</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>90865500</v>
+      </c>
+      <c r="E58" s="3">
         <v>84839000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>82313300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>86234800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>71321700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>77677100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>68628000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>72309400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>53305700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>67692000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>53642500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>51580000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>15312400</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>38286000</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>63067400</v>
+      </c>
+      <c r="E59" s="3">
         <v>28161500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>48304300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>22971900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>38063600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>19862600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>35996100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>18076800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>34729800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12581500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>31597800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14642200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>33155400</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R59" s="3">
         <v>33785900</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>274866300</v>
+      </c>
+      <c r="E60" s="3">
         <v>245197500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>223055100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>218046900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>185009500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>182476300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>166482500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>147159500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>139848400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>124531800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>137397100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>135634200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>106064100</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q60" s="3">
+      <c r="Q60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R60" s="3">
         <v>128108800</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>34506900</v>
+      </c>
+      <c r="E61" s="3">
         <v>29230100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>26729700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>20093400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>22280100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>20383600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>26113900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>23526700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>25820100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>23025000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>28250500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>20864400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>53102200</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>23091800</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1507500</v>
+      </c>
+      <c r="E62" s="3">
         <v>1647400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1124200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1374700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1486800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1270300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>668000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>34507500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>694700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>29897000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>487600</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P62" s="3">
         <v>633400</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q62" s="3">
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R62" s="3">
         <v>380900</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3068,8 +3216,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3115,8 +3266,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3162,55 +3316,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>311052400</v>
+      </c>
+      <c r="E66" s="3">
         <v>276106800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>251069500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>239565900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>208940300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>204168900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>193440900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>205253900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>166581200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>177470500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>166292000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>156944500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>160374200</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q66" s="3">
+      <c r="Q66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R66" s="3">
         <v>152269200</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3228,8 +3388,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3275,8 +3436,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3322,8 +3486,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3369,8 +3536,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3416,55 +3586,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>28160200</v>
+      </c>
+      <c r="E72" s="3">
         <v>26818000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>25018900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>24322200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>22944500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>22278000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>21292000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>22009700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>20433600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>20791500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>20496800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>19486200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>18918400</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R72" s="3">
         <v>19342300</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3510,8 +3686,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3557,8 +3736,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3604,55 +3786,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>51677700</v>
+      </c>
+      <c r="E76" s="3">
         <v>48506800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>45740900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>44250000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>42635700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>41678300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>40156800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>40846100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>38430600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>38903200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>37913300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>35970000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>35555500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>36848300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>36698700</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3698,60 +3886,66 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3797,8 +3991,11 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3816,55 +4013,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E83" s="3">
+      <c r="D83" s="3">
+        <v>118300</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3">
         <v>237200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>-138500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>118200</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3">
         <v>220700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>-121500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>101000</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N83" s="3">
         <v>195700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>-111200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>97100</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R83" s="3">
         <v>200200</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3910,8 +4111,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3957,8 +4161,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4004,8 +4211,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4051,8 +4261,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4098,55 +4311,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4483900</v>
+      </c>
+      <c r="E89" s="3">
         <v>10897000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2559500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3631700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>11684800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7353400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>8076100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>10860700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4549800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>9763200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1898100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-8895200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1766900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-321000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2431900</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4164,55 +4383,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-53600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-35500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-99100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-37100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-49500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-25200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-84100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-32100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-34400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-28300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-91200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-46900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-30300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-53900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-68900</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4258,8 +4481,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4305,55 +4531,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>2706600</v>
+      </c>
+      <c r="E94" s="3">
         <v>740400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5936500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>382300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>738900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>3654400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4842600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>567500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-858000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5077500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4397500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>1787000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-75300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>71600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4353200</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4371,55 +4603,59 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1025500</v>
+      </c>
+      <c r="E96" s="3">
         <v>952400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>263400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>843800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>211100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>319800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>760300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1305800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>197200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>253200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>114800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>1300300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>237500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>259900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>199000</v>
       </c>
     </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4465,8 +4701,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4512,8 +4751,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4559,145 +4801,157 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3498600</v>
+      </c>
+      <c r="E100" s="3">
         <v>4312500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2816600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>7567800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2001300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-573000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1179200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1069400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2074300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-193100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>5010600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1527300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>50300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3425600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3388200</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-22200</v>
+      </c>
+      <c r="E101" s="3">
         <v>14600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>60200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-4400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-5200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-17400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>20100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-61800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>148000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-53300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-217400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>330700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>22900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-71000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-23800</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>10643000</v>
+      </c>
+      <c r="E102" s="3">
         <v>15916800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-597300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>11538700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>10400200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4257300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>4472800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>10354500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-7487300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4475100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2531300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-8697400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1889800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3122900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-5527000</v>
       </c>
     </row>
